--- a/docs/oc-regiones/alimentos/aysen.xlsx
+++ b/docs/oc-regiones/alimentos/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M259"/>
+  <dimension ref="A1:M260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6602.03</v>
+        <v>6546.11</v>
       </c>
     </row>
     <row r="3">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4310.11</v>
+        <v>4273.61</v>
       </c>
     </row>
     <row r="4">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1015.75</v>
+        <v>1005.61</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1966.32</v>
+        <v>1946.7</v>
       </c>
     </row>
     <row r="6">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2420.82</v>
+        <v>2396.66</v>
       </c>
     </row>
     <row r="7">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1343.81</v>
+        <v>1330.4</v>
       </c>
     </row>
     <row r="8">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>30959.63</v>
+        <v>30635.42</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2664.84</v>
+        <v>2636.93</v>
       </c>
     </row>
     <row r="10">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1978.34</v>
+        <v>1967.52</v>
       </c>
     </row>
     <row r="11">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1420.33</v>
+        <v>1412.57</v>
       </c>
     </row>
     <row r="12">
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1174.63</v>
+        <v>1168.21</v>
       </c>
     </row>
     <row r="13">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2262.02</v>
+        <v>2249.65</v>
       </c>
     </row>
     <row r="14">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1308.68</v>
+        <v>1301.53</v>
       </c>
     </row>
     <row r="15">
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1099.5</v>
+        <v>1093.49</v>
       </c>
     </row>
     <row r="16">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3907.68</v>
+        <v>3886.32</v>
       </c>
     </row>
     <row r="17">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1009.65</v>
+        <v>998.4</v>
       </c>
     </row>
     <row r="18">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>782.97</v>
+        <v>774.24</v>
       </c>
     </row>
     <row r="19">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6086.92</v>
+        <v>6019.11</v>
       </c>
     </row>
     <row r="20">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>750.92</v>
+        <v>742.55</v>
       </c>
     </row>
     <row r="21">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1845.99</v>
+        <v>1843.64</v>
       </c>
     </row>
     <row r="22">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2348.53</v>
+        <v>2345.54</v>
       </c>
     </row>
     <row r="23">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1694.52</v>
+        <v>1692.37</v>
       </c>
     </row>
     <row r="24">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3727.7</v>
+        <v>3768.24</v>
       </c>
     </row>
     <row r="25">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1224.54</v>
+        <v>1233.02</v>
       </c>
     </row>
     <row r="26">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2103.11</v>
+        <v>2117.68</v>
       </c>
     </row>
     <row r="27">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1150.21</v>
+        <v>1148.42</v>
       </c>
     </row>
     <row r="28">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>748.71</v>
+        <v>752.58</v>
       </c>
     </row>
     <row r="29">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9902.870000000001</v>
+        <v>9954.01</v>
       </c>
     </row>
     <row r="30">
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5171.27</v>
+        <v>5197.97</v>
       </c>
     </row>
     <row r="31">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>823.24</v>
+        <v>827.49</v>
       </c>
     </row>
     <row r="32">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3770.98</v>
+        <v>3790.45</v>
       </c>
     </row>
     <row r="33">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3074.82</v>
+        <v>3090.7</v>
       </c>
     </row>
     <row r="34">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4936.08</v>
+        <v>4970.92</v>
       </c>
     </row>
     <row r="35">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1015.75</v>
+        <v>1022.92</v>
       </c>
     </row>
     <row r="36">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>904.6799999999999</v>
+        <v>911.0599999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1663.2</v>
+        <v>1674.94</v>
       </c>
     </row>
     <row r="38">
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1940.52</v>
+        <v>1954.21</v>
       </c>
     </row>
     <row r="39">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1693.51</v>
+        <v>1705.46</v>
       </c>
     </row>
     <row r="40">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1693.51</v>
+        <v>1705.46</v>
       </c>
     </row>
     <row r="41">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3071.17</v>
+        <v>3092.85</v>
       </c>
     </row>
     <row r="42">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4454.31</v>
+        <v>4485.75</v>
       </c>
     </row>
     <row r="43">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2500.24</v>
+        <v>2517.88</v>
       </c>
     </row>
     <row r="44">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2838.47</v>
+        <v>2801.78</v>
       </c>
     </row>
     <row r="45">
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1673.37</v>
+        <v>1651.74</v>
       </c>
     </row>
     <row r="46">
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2055.39</v>
+        <v>2034.94</v>
       </c>
     </row>
     <row r="47">
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>784.13</v>
+        <v>782.4299999999999</v>
       </c>
     </row>
     <row r="48">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>770</v>
+        <v>766.77</v>
       </c>
     </row>
     <row r="49">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1427.92</v>
+        <v>1421.93</v>
       </c>
     </row>
     <row r="50">
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1493.58</v>
+        <v>1487.32</v>
       </c>
     </row>
     <row r="51">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>787.34</v>
+        <v>780.67</v>
       </c>
     </row>
     <row r="52">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2165.55</v>
+        <v>2147.21</v>
       </c>
     </row>
     <row r="53">
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>760.95</v>
+        <v>760.34</v>
       </c>
     </row>
     <row r="54">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>761</v>
+        <v>763.92</v>
       </c>
     </row>
     <row r="55">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2195.92</v>
+        <v>2205.87</v>
       </c>
     </row>
     <row r="56">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1777.66</v>
+        <v>1775.17</v>
       </c>
     </row>
     <row r="57">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2294.1</v>
+        <v>2309.89</v>
       </c>
     </row>
     <row r="58">
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>961.1</v>
+        <v>967.72</v>
       </c>
     </row>
     <row r="59">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1832.08</v>
+        <v>1796.35</v>
       </c>
     </row>
     <row r="60">
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1822.42</v>
+        <v>1786.88</v>
       </c>
     </row>
     <row r="61">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>832.72</v>
+        <v>816.48</v>
       </c>
     </row>
     <row r="62">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2015.53</v>
+        <v>1976.22</v>
       </c>
     </row>
     <row r="63">
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1466.3</v>
+        <v>1445.28</v>
       </c>
     </row>
     <row r="64">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3855.05</v>
+        <v>3799.8</v>
       </c>
     </row>
     <row r="65">
@@ -4396,13 +4396,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1784.06</v>
+        <v>1761.42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1403-5-CM26</t>
+          <t>1403-6-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>931.71</v>
+        <v>1598.57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1403-6-CM26</t>
+          <t>1403-5-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1619.12</v>
+        <v>919.88</v>
       </c>
     </row>
     <row r="68">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1829.45</v>
+        <v>1825.85</v>
       </c>
     </row>
     <row r="69">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>915.59</v>
+        <v>915.6</v>
       </c>
     </row>
     <row r="70">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5401.42</v>
+        <v>5397.73</v>
       </c>
     </row>
     <row r="71">
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1232.73</v>
+        <v>1231.88</v>
       </c>
     </row>
     <row r="72">
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2265.25</v>
+        <v>2253.28</v>
       </c>
     </row>
     <row r="73">
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>7118.59</v>
+        <v>7214.45</v>
       </c>
     </row>
     <row r="74">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3396.47</v>
+        <v>3442.21</v>
       </c>
     </row>
     <row r="75">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1246.71</v>
+        <v>1263.5</v>
       </c>
     </row>
     <row r="76">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2601.36</v>
+        <v>2640.96</v>
       </c>
     </row>
     <row r="77">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3075.59</v>
+        <v>3122.41</v>
       </c>
     </row>
     <row r="78">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2908.8</v>
+        <v>2898.44</v>
       </c>
     </row>
     <row r="79">
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1995.99</v>
+        <v>1988.88</v>
       </c>
     </row>
     <row r="80">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1734.83</v>
+        <v>1728.66</v>
       </c>
     </row>
     <row r="81">
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3699.22</v>
+        <v>3671.54</v>
       </c>
     </row>
     <row r="82">
@@ -5433,13 +5433,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3262.61</v>
+        <v>3238.19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1173435-5-CM26</t>
+          <t>1426103-11-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>73.182.900-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5494,13 +5494,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1309.83</v>
+        <v>1908.91</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1426103-11-CM26</t>
+          <t>1173435-5-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>73.182.900-4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Centro de Educación y Trabajo XI Región</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1923.31</v>
+        <v>1300.03</v>
       </c>
     </row>
     <row r="85">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3951.67</v>
+        <v>3972.08</v>
       </c>
     </row>
     <row r="86">
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>809.09</v>
+        <v>813.27</v>
       </c>
     </row>
     <row r="87">
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1138.3</v>
+        <v>1133.5</v>
       </c>
     </row>
     <row r="88">
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1062.59</v>
+        <v>1058.11</v>
       </c>
     </row>
     <row r="89">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2522.47</v>
+        <v>2511.83</v>
       </c>
     </row>
     <row r="90">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2686.25</v>
+        <v>2710.68</v>
       </c>
     </row>
     <row r="91">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>979.9400000000001</v>
+        <v>988.86</v>
       </c>
     </row>
     <row r="92">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2172.51</v>
+        <v>2192.28</v>
       </c>
     </row>
     <row r="93">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>6317.77</v>
+        <v>6375.23</v>
       </c>
     </row>
     <row r="94">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4336.57</v>
+        <v>4366.77</v>
       </c>
     </row>
     <row r="95">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1734.68</v>
+        <v>1746.1</v>
       </c>
     </row>
     <row r="96">
@@ -6287,13 +6287,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1935.04</v>
+        <v>1931.72</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1403-84-CM26</t>
+          <t>1403-85-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6333,12 +6333,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>857.78</v>
+        <v>3035.22</v>
       </c>
     </row>
     <row r="98">
@@ -6409,13 +6409,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3818.06</v>
+        <v>3811.52</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1403-85-CM26</t>
+          <t>1403-84-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3040.43</v>
+        <v>856.3099999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4457.83</v>
+        <v>4433.55</v>
       </c>
     </row>
     <row r="101">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1151.35</v>
+        <v>1144.35</v>
       </c>
     </row>
     <row r="102">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6030.76</v>
+        <v>6007.48</v>
       </c>
     </row>
     <row r="103">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1795.95</v>
+        <v>1805.24</v>
       </c>
     </row>
     <row r="104">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2628.39</v>
+        <v>2744.46</v>
       </c>
     </row>
     <row r="105">
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>936.0599999999999</v>
+        <v>963.25</v>
       </c>
     </row>
     <row r="106">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3247.06</v>
+        <v>3341.38</v>
       </c>
     </row>
     <row r="107">
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2379.71</v>
+        <v>2389.09</v>
       </c>
     </row>
     <row r="108">
@@ -7019,7 +7019,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2664.73</v>
+        <v>2675.24</v>
       </c>
     </row>
     <row r="109">
@@ -7080,13 +7080,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2453.01</v>
+        <v>2462.68</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>951405-46-CM26</t>
+          <t>3431-21-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>19326.49</v>
+        <v>1108.72</v>
       </c>
     </row>
     <row r="111">
@@ -7202,13 +7202,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1000.33</v>
+        <v>1016.82</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3431-21-CM26</t>
+          <t>3431-20-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7263,13 +7263,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1090.74</v>
+        <v>1102.21</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2713-249-CM26</t>
+          <t>951405-46-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3216.97</v>
+        <v>19645.02</v>
       </c>
     </row>
     <row r="114">
@@ -7385,13 +7385,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6035.49</v>
+        <v>6134.96</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3431-20-CM26</t>
+          <t>2713-249-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1084.34</v>
+        <v>3269.99</v>
       </c>
     </row>
     <row r="116">
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>981.21</v>
+        <v>983.63</v>
       </c>
     </row>
     <row r="117">
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3165.21</v>
+        <v>3172.99</v>
       </c>
     </row>
     <row r="118">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2751.96</v>
+        <v>2758.73</v>
       </c>
     </row>
     <row r="119">
@@ -7690,13 +7690,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1560.55</v>
+        <v>1549.54</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1403-137-CM26</t>
+          <t>3431-24-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7751,13 +7751,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>794.6900000000001</v>
+        <v>18145.11</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>655348-27-CM26</t>
+          <t>3431-25-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7797,12 +7797,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7812,13 +7812,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2014</v>
+        <v>3104.49</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1403-138-CM26</t>
+          <t>655348-27-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7873,13 +7873,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>981.73</v>
+        <v>2050.51</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3431-24-CM26</t>
+          <t>1403-137-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>17821.98</v>
+        <v>809.09</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3431-25-CM26</t>
+          <t>1403-138-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -7995,13 +7995,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3049.21</v>
+        <v>999.53</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3431-34-CM26</t>
+          <t>3431-33-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>Distribuidora Surmontt</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>76.287.477-6</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8056,13 +8056,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>4835.93</v>
+        <v>1441.63</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3431-36-CM26</t>
+          <t>3431-34-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8117,13 +8117,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2684.74</v>
+        <v>4911.68</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3431-33-CM26</t>
+          <t>3431-36-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Distribuidora Surmontt</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.287.477-6</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1419.4</v>
+        <v>2726.79</v>
       </c>
     </row>
     <row r="128">
@@ -8239,13 +8239,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2364.1</v>
+        <v>2363.98</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1079689-92-CM26</t>
+          <t>1403-153-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8300,13 +8300,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>8135.31</v>
+        <v>1948.08</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1403-153-CM26</t>
+          <t>1079689-92-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8346,12 +8346,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8361,7 +8361,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1948.18</v>
+        <v>8134.89</v>
       </c>
     </row>
     <row r="131">
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1318.67</v>
+        <v>1312.77</v>
       </c>
     </row>
     <row r="132">
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1247.62</v>
+        <v>1248.69</v>
       </c>
     </row>
     <row r="133">
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>902.85</v>
+        <v>906.58</v>
       </c>
     </row>
     <row r="134">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2468.12</v>
+        <v>2478.32</v>
       </c>
     </row>
     <row r="135">
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1881.89</v>
+        <v>1889.67</v>
       </c>
     </row>
     <row r="136">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1245.04</v>
+        <v>1250.18</v>
       </c>
     </row>
     <row r="137">
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>801.6799999999999</v>
+        <v>792.42</v>
       </c>
     </row>
     <row r="138">
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1218.88</v>
+        <v>1200.7</v>
       </c>
     </row>
     <row r="139">
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2874.66</v>
+        <v>2858.14</v>
       </c>
     </row>
     <row r="140">
@@ -8971,7 +8971,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3159.09</v>
+        <v>3138.85</v>
       </c>
     </row>
     <row r="141">
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1056.66</v>
+        <v>1052.11</v>
       </c>
     </row>
     <row r="142">
@@ -9093,13 +9093,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2036.61</v>
+        <v>1989.22</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1079689-119-CM26</t>
+          <t>1079689-118-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9154,13 +9154,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>5034.74</v>
+        <v>4572.71</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1426103-25-CM26</t>
+          <t>1079689-119-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9215,13 +9215,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2407.09</v>
+        <v>4874.2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1079689-118-CM26</t>
+          <t>1426103-25-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9241,17 +9241,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">RODOLFO </t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4723.32</v>
+        <v>2330.34</v>
       </c>
     </row>
     <row r="146">
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2038.37</v>
+        <v>1998.17</v>
       </c>
     </row>
     <row r="147">
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>780.28</v>
+        <v>766.13</v>
       </c>
     </row>
     <row r="148">
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>791.15</v>
+        <v>776.8</v>
       </c>
     </row>
     <row r="149">
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>790.01</v>
+        <v>775.6799999999999</v>
       </c>
     </row>
     <row r="150">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1501.29</v>
+        <v>1461.09</v>
       </c>
     </row>
     <row r="151">
@@ -9642,7 +9642,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2143.28</v>
+        <v>2085.89</v>
       </c>
     </row>
     <row r="152">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>4217.03</v>
+        <v>4104.11</v>
       </c>
     </row>
     <row r="153">
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>6381.66</v>
+        <v>6400.23</v>
       </c>
     </row>
     <row r="154">
@@ -9825,7 +9825,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>68419.44</v>
+        <v>68618.61</v>
       </c>
     </row>
     <row r="155">
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3480.73</v>
+        <v>3495.19</v>
       </c>
     </row>
     <row r="156">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2148.46</v>
+        <v>2157.39</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1173437-5-CM26</t>
+          <t>1426103-29-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.959.200-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>BIDFOOD CHILE S.A.</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.111.152-3</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10008,13 +10008,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3332.05</v>
+        <v>2012.69</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1426103-29-CM26</t>
+          <t>1426103-30-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10054,12 +10054,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10069,13 +10069,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1995.75</v>
+        <v>1181.96</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1426103-30-CM26</t>
+          <t>1173437-5-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10100,12 +10100,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.959.200-K</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Centro de Educación y Trabajo Puerto Aysén</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>BIDFOOD CHILE S.A.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.111.152-3</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1172.02</v>
+        <v>3360.33</v>
       </c>
     </row>
     <row r="160">
@@ -10191,7 +10191,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2339.27</v>
+        <v>2359.13</v>
       </c>
     </row>
     <row r="161">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>875.3099999999999</v>
+        <v>873.85</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1403-261-CM26</t>
+          <t>1403-265-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10313,13 +10313,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>793.2</v>
+        <v>2485.16</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1403-265-CM26</t>
+          <t>1403-261-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10374,7 +10374,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2454.95</v>
+        <v>802.96</v>
       </c>
     </row>
     <row r="164">
@@ -10435,7 +10435,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1983.4</v>
+        <v>2009.81</v>
       </c>
     </row>
     <row r="165">
@@ -10496,7 +10496,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>5248.16</v>
+        <v>5316.64</v>
       </c>
     </row>
     <row r="166">
@@ -10557,7 +10557,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1578.03</v>
+        <v>1595.97</v>
       </c>
     </row>
     <row r="167">
@@ -10618,7 +10618,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1667.49</v>
+        <v>1686.45</v>
       </c>
     </row>
     <row r="168">
@@ -10679,7 +10679,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>14954.06</v>
+        <v>15088.77</v>
       </c>
     </row>
     <row r="169">
@@ -10740,13 +10740,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>891.38</v>
+        <v>894.1799999999999</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3431-55-CM26</t>
+          <t>1403-303-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10771,12 +10771,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10801,13 +10801,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>794.98</v>
+        <v>2243.98</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1403-303-CM26</t>
+          <t>3431-55-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10832,12 +10832,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10862,7 +10862,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2234.72</v>
+        <v>798.28</v>
       </c>
     </row>
     <row r="172">
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3218.64</v>
+        <v>3225.31</v>
       </c>
     </row>
     <row r="173">
@@ -10984,7 +10984,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>830.72</v>
+        <v>827.15</v>
       </c>
     </row>
     <row r="174">
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2504.21</v>
+        <v>2470.17</v>
       </c>
     </row>
     <row r="175">
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1515.83</v>
+        <v>1495.22</v>
       </c>
     </row>
     <row r="176">
@@ -11167,7 +11167,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2656.97</v>
+        <v>2634.31</v>
       </c>
     </row>
     <row r="177">
@@ -11228,13 +11228,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2258.33</v>
+        <v>2239.07</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1403-315-CM26</t>
+          <t>1403-334-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11289,13 +11289,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1846.96</v>
+        <v>1944.01</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1403-317-CM26</t>
+          <t>1403-318-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11350,13 +11350,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1879.84</v>
+        <v>2932.24</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1403-318-CM26</t>
+          <t>1403-315-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11411,13 +11411,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2916.53</v>
+        <v>1856.9</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1403-334-CM26</t>
+          <t>1403-317-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1933.6</v>
+        <v>1889.97</v>
       </c>
     </row>
     <row r="182">
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2246.05</v>
+        <v>2271.17</v>
       </c>
     </row>
     <row r="183">
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>20362.56</v>
+        <v>20590.29</v>
       </c>
     </row>
     <row r="184">
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3284.74</v>
+        <v>3321.48</v>
       </c>
     </row>
     <row r="185">
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>829.35</v>
+        <v>835.63</v>
       </c>
     </row>
     <row r="186">
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1044.47</v>
+        <v>1048.43</v>
       </c>
     </row>
     <row r="187">
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1043.12</v>
+        <v>1040.48</v>
       </c>
     </row>
     <row r="188">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1787.97</v>
+        <v>1783.46</v>
       </c>
     </row>
     <row r="189">
@@ -11960,7 +11960,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>3504.5</v>
+        <v>3489.14</v>
       </c>
     </row>
     <row r="190">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1046.76</v>
+        <v>1042.17</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1173435-22-CM26</t>
+          <t>1403-354-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12052,12 +12052,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>73.182.900-4</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12067,12 +12067,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12082,13 +12082,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1778.78</v>
+        <v>1898.98</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1403-354-CM26</t>
+          <t>1173435-22-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12113,12 +12113,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>73.182.900-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>Centro de Educación y Trabajo XI Región</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1919.86</v>
+        <v>1759.43</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1403-367-CM26</t>
+          <t>4778-292-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12204,13 +12204,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1773.03</v>
+        <v>7844.22</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4778-292-CM26</t>
+          <t>1403-367-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12235,12 +12235,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12250,12 +12250,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12265,13 +12265,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>7863.64</v>
+        <v>1768.65</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>418-1638-CM26</t>
+          <t>1403-373-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12326,13 +12326,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>845.91</v>
+        <v>1056.31</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1403-373-CM26</t>
+          <t>418-1638-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12357,12 +12357,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1052.82</v>
+        <v>848.71</v>
       </c>
     </row>
     <row r="197">
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2707.42</v>
+        <v>2716.03</v>
       </c>
     </row>
     <row r="198">
@@ -12509,7 +12509,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2694.65</v>
+        <v>2703.23</v>
       </c>
     </row>
     <row r="199">
@@ -12570,7 +12570,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3097.54</v>
+        <v>3107.4</v>
       </c>
     </row>
     <row r="200">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1429.19</v>
+        <v>1445.96</v>
       </c>
     </row>
     <row r="201">
@@ -12692,7 +12692,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>997.47</v>
+        <v>1014.34</v>
       </c>
     </row>
     <row r="202">
@@ -12753,13 +12753,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2100.81</v>
+        <v>2136.34</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1403-410-CM26</t>
+          <t>1173435-23-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12784,12 +12784,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>73.182.900-4</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>Centro de Educación y Trabajo XI Región</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12814,13 +12814,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2724.74</v>
+        <v>808.39</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1173435-23-CM26</t>
+          <t>1403-412-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>73.182.900-4</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12875,13 +12875,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>800.88</v>
+        <v>2206.64</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1403-412-CM26</t>
+          <t>1403-410-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12921,12 +12921,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12936,7 +12936,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2186.14</v>
+        <v>2750.3</v>
       </c>
     </row>
     <row r="206">
@@ -12997,13 +12997,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3098.47</v>
+        <v>3074.96</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1403-425-CM26</t>
+          <t>1403-416-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2297.37</v>
+        <v>794.23</v>
       </c>
     </row>
     <row r="208">
@@ -13119,13 +13119,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2661.88</v>
+        <v>2616.9</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1403-416-CM26</t>
+          <t>1403-425-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>807.88</v>
+        <v>2258.55</v>
       </c>
     </row>
     <row r="210">
@@ -13241,13 +13241,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>906.79</v>
+        <v>893.92</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>418-1865-CM26</t>
+          <t>1426103-52-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13302,13 +13302,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1124.3</v>
+        <v>3111.37</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>951405-225-CM26</t>
+          <t>1426103-54-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13328,17 +13328,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13348,12 +13348,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>9363.35</v>
+        <v>1426.23</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>951405-227-CM26</t>
+          <t>1426103-53-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13389,17 +13389,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13424,13 +13424,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>961.9400000000001</v>
+        <v>1660.73</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>655348-54-CM26</t>
+          <t>1426103-51-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13455,12 +13455,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13485,13 +13485,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1133.05</v>
+        <v>6335.87</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1426103-51-CM26</t>
+          <t>418-1865-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13546,13 +13546,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>6424.14</v>
+        <v>1108.85</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1426103-52-CM26</t>
+          <t>951405-227-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13607,13 +13607,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3154.72</v>
+        <v>948.72</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1426103-53-CM26</t>
+          <t>951405-225-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13633,17 +13633,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13653,12 +13653,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13668,13 +13668,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1683.87</v>
+        <v>9234.690000000001</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1426103-54-CM26</t>
+          <t>655348-54-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13694,17 +13694,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13714,12 +13714,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13729,7 +13729,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1446.1</v>
+        <v>1117.48</v>
       </c>
     </row>
     <row r="219">
@@ -13790,13 +13790,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3415.52</v>
+        <v>3394.35</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1403-450-CM26</t>
+          <t>1403-452-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13836,12 +13836,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13851,13 +13851,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1400.07</v>
+        <v>1483.19</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3431-108-CM26</t>
+          <t>4778-307-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13882,12 +13882,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13897,12 +13897,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t xml:space="preserve">RODOLFO </t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13912,13 +13912,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>3192.99</v>
+        <v>4231.2</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1403-452-CM26</t>
+          <t>4778-308-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13958,12 +13958,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>sociedad de nutricionistas nutrihouse ltda.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.095.459-4</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13973,13 +13973,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1450.48</v>
+        <v>2145.56</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4778-308-CM26</t>
+          <t>4778-324-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14019,12 +14019,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>sociedad de nutricionistas nutrihouse ltda.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.095.459-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14034,13 +14034,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2098.24</v>
+        <v>4929.83</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>4778-324-CM26</t>
+          <t>3431-108-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14065,12 +14065,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14095,13 +14095,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>4821.1</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4778-307-CM26</t>
+          <t>1403-450-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14126,12 +14126,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14156,7 +14156,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4137.88</v>
+        <v>1431.64</v>
       </c>
     </row>
     <row r="226">
@@ -14217,13 +14217,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1169</v>
+        <v>1172.62</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1403-469-CM26</t>
+          <t>1173437-9-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14248,12 +14248,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.959.200-K</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>Centro de Educación y Trabajo Puerto Aysén</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14263,12 +14263,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>BIDFOOD CHILE S.A.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.111.152-3</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14278,13 +14278,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2126.84</v>
+        <v>3069.29</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1173437-9-CM26</t>
+          <t>1403-469-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14309,12 +14309,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.959.200-K</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14324,12 +14324,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>BIDFOOD CHILE S.A.</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.111.152-3</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14339,7 +14339,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3110.72</v>
+        <v>2098.51</v>
       </c>
     </row>
     <row r="229">
@@ -14400,7 +14400,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1669.44</v>
+        <v>1685.3</v>
       </c>
     </row>
     <row r="230">
@@ -14461,13 +14461,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>779.45</v>
+        <v>787.26</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1426103-62-CM26</t>
+          <t>1426103-61-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14507,12 +14507,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t xml:space="preserve">RODOLFO </t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14522,13 +14522,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1919.41</v>
+        <v>1129.65</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1426103-61-CM26</t>
+          <t>1426103-62-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1118.45</v>
+        <v>1938.63</v>
       </c>
     </row>
     <row r="233">
@@ -14644,7 +14644,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>837.65</v>
+        <v>841.92</v>
       </c>
     </row>
     <row r="234">
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2278.47</v>
+        <v>2290.08</v>
       </c>
     </row>
     <row r="235">
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>772.52</v>
+        <v>776.46</v>
       </c>
     </row>
     <row r="236">
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2896.31</v>
+        <v>2907.59</v>
       </c>
     </row>
     <row r="237">
@@ -14888,7 +14888,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1137.21</v>
+        <v>1141.63</v>
       </c>
     </row>
     <row r="238">
@@ -14949,13 +14949,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1120.72</v>
+        <v>1123.11</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1403-534-CM26</t>
+          <t>1403-530-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14995,12 +14995,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15010,7 +15010,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2889.39</v>
+        <v>3777.09</v>
       </c>
     </row>
     <row r="240">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>839.98</v>
+        <v>841.77</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1403-530-CM26</t>
+          <t>1403-534-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15132,7 +15132,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3769.06</v>
+        <v>2895.55</v>
       </c>
     </row>
     <row r="242">
@@ -15193,7 +15193,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2911.63</v>
+        <v>2930.61</v>
       </c>
     </row>
     <row r="243">
@@ -15254,7 +15254,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1773.97</v>
+        <v>1778.04</v>
       </c>
     </row>
     <row r="244">
@@ -15315,7 +15315,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1269.31</v>
+        <v>1277.81</v>
       </c>
     </row>
     <row r="245">
@@ -15376,7 +15376,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>770.34</v>
+        <v>775.5</v>
       </c>
     </row>
     <row r="246">
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1278.94</v>
+        <v>1274.9</v>
       </c>
     </row>
     <row r="247">
@@ -15498,7 +15498,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1260.87</v>
+        <v>1258.13</v>
       </c>
     </row>
     <row r="248">
@@ -15559,7 +15559,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1571.5</v>
+        <v>1562.4</v>
       </c>
     </row>
     <row r="249">
@@ -15620,7 +15620,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3854.88</v>
+        <v>3832.57</v>
       </c>
     </row>
     <row r="250">
@@ -15681,7 +15681,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>17374.92</v>
+        <v>17094.53</v>
       </c>
     </row>
     <row r="251">
@@ -15742,7 +15742,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>4122.82</v>
+        <v>4099.96</v>
       </c>
     </row>
     <row r="252">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2170.07</v>
+        <v>2158.04</v>
       </c>
     </row>
     <row r="253">
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2236.18</v>
+        <v>2223.79</v>
       </c>
     </row>
     <row r="254">
@@ -15925,7 +15925,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>777.98</v>
+        <v>773.66</v>
       </c>
     </row>
     <row r="255">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>4779.97</v>
+        <v>4756.46</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1403-590-CM26</t>
+          <t>1403-591-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>BIDFOOD CHILE S.A.</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.111.152-3</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16047,13 +16047,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2537.11</v>
+        <v>3076.47</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1403-591-CM26</t>
+          <t>655348-70-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16078,12 +16078,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16093,12 +16093,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>BIDFOOD CHILE S.A.</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>76.111.152-3</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16108,7 +16108,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3056.02</v>
+        <v>1019.93</v>
       </c>
     </row>
     <row r="258">
@@ -16169,13 +16169,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1796.17</v>
+        <v>1808.19</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>655348-70-CM26</t>
+          <t>1403-590-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16200,12 +16200,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16230,7 +16230,68 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1013.15</v>
+        <v>2554.09</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1079689-335-CM26</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>81.094.100-6</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="n">
+        <v>2482.17</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/alimentos/aysen.xlsx
+++ b/docs/oc-regiones/alimentos/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M485"/>
+  <dimension ref="A1:M508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8322,7 +8322,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1403-4047-CM25</t>
+          <t>1403-4044-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>Distribuidora Surmontt</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.287.477-6</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1853.51</v>
+        <v>1647.15</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1403-4044-CM25</t>
+          <t>1403-4045-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Distribuidora Surmontt</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.287.477-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1647.15</v>
+        <v>2432.63</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1403-4045-CM25</t>
+          <t>1403-4046-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2432.63</v>
+        <v>1088.46</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1403-4046-CM25</t>
+          <t>1403-4047-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1088.46</v>
+        <v>1853.51</v>
       </c>
     </row>
     <row r="134">
@@ -8993,7 +8993,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1403-4064-CM25</t>
+          <t>951405-297-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1207.49</v>
+        <v>8641.459999999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>951405-297-CM25</t>
+          <t>1403-4064-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>8641.459999999999</v>
+        <v>1207.49</v>
       </c>
     </row>
     <row r="143">
@@ -9481,7 +9481,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1403-4092-CM25</t>
+          <t>1403-4094-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2260.65</v>
+        <v>5680.41</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1426103-161-CM25</t>
+          <t>1403-4092-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1861.91</v>
+        <v>2260.65</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1426103-160-CM25</t>
+          <t>1426103-161-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodolfo </t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2511.36</v>
+        <v>1861.91</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1426103-162-CM25</t>
+          <t>1426103-160-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>779.62</v>
+        <v>2511.36</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1403-4094-CM25</t>
+          <t>1426103-162-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>5680.41</v>
+        <v>779.62</v>
       </c>
     </row>
     <row r="154">
@@ -9847,7 +9847,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1403-4116-CM25</t>
+          <t>1403-4111-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2838.74</v>
+        <v>2241.76</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1403-4111-CM25</t>
+          <t>1403-4116-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2241.76</v>
+        <v>2838.74</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>418-2957-CM25</t>
+          <t>1079689-297-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1660.97</v>
+        <v>1852.98</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1079689-295-CM25</t>
+          <t>1079689-298-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>906.01</v>
+        <v>4177.77</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1079689-296-CM25</t>
+          <t>1079689-295-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2188.67</v>
+        <v>906.01</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1079689-297-CM25</t>
+          <t>418-2957-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1852.98</v>
+        <v>1660.97</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1079689-298-CM25</t>
+          <t>1079689-296-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4177.77</v>
+        <v>2188.67</v>
       </c>
     </row>
     <row r="162">
@@ -11494,7 +11494,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1272253-10-CM25</t>
+          <t>1403-4195-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11514,12 +11514,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>65.239.010-2</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>747.39</v>
+        <v>3273.75</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1403-4195-CM25</t>
+          <t>1272253-10-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11575,12 +11575,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>65.239.010-2</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3273.75</v>
+        <v>747.39</v>
       </c>
     </row>
     <row r="184">
@@ -11799,7 +11799,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1403-4222-CM25</t>
+          <t>1426103-188-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2136.78</v>
+        <v>1939.36</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1403-4223-CM25</t>
+          <t>1426103-187-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1150.85</v>
+        <v>4037.45</v>
       </c>
     </row>
     <row r="189">
@@ -11982,7 +11982,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1426103-187-CM25</t>
+          <t>1426103-189-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>4037.45</v>
+        <v>5050.98</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1426103-188-CM25</t>
+          <t>1403-4222-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1939.36</v>
+        <v>2136.78</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1426103-189-CM25</t>
+          <t>1403-4223-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>5050.98</v>
+        <v>1150.85</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>418-3400-CM25</t>
+          <t>418-3401-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12220,13 +12220,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2483.68</v>
+        <v>962.09</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1691-2740-CM25</t>
+          <t>418-3400-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1282.64</v>
+        <v>2483.68</v>
       </c>
     </row>
     <row r="195">
@@ -12348,7 +12348,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>418-3401-CM25</t>
+          <t>1691-2740-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>962.09</v>
+        <v>1282.64</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>655348-85-CM25</t>
+          <t>655348-83-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>799.33</v>
+        <v>5853.17</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1173437-20-CM25</t>
+          <t>1403-4234-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.959.200-K</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2602</v>
+        <v>1426.62</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1403-4234-CM25</t>
+          <t>1173437-20-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.959.200-K</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1426.62</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>655348-83-CM25</t>
+          <t>655348-85-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>5853.17</v>
+        <v>799.33</v>
       </c>
     </row>
     <row r="201">
@@ -12803,7 +12803,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H203" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -12860,7 +12864,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H204" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -12889,7 +12897,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1403-4264-CM25</t>
+          <t>1403-4261-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12919,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12929,12 +12937,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12944,13 +12952,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2396.66</v>
+        <v>1005.61</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1403-4261-CM25</t>
+          <t>1426103-195-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12975,12 +12983,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -12990,12 +12998,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13005,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1005.61</v>
+        <v>1946.7</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1426103-195-CM25</t>
+          <t>1403-4264-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13036,12 +13044,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13051,12 +13059,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13066,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1946.7</v>
+        <v>2396.66</v>
       </c>
     </row>
     <row r="208">
@@ -13133,7 +13141,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>951405-373-CM25</t>
+          <t>951405-372-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13161,7 +13169,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H209" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -13169,12 +13181,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13184,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2636.93</v>
+        <v>30635.42</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>951405-372-CM25</t>
+          <t>951405-373-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13218,7 +13230,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H210" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -13226,12 +13242,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13241,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>30635.42</v>
+        <v>2636.93</v>
       </c>
     </row>
     <row r="211">
@@ -13308,7 +13324,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1691-2855-CM25</t>
+          <t>1079689-361-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13333,12 +13349,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13348,12 +13364,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13363,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1301.53</v>
+        <v>3886.32</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1079689-361-CM25</t>
+          <t>1691-2855-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13394,12 +13410,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13409,12 +13425,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13424,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3886.32</v>
+        <v>1301.53</v>
       </c>
     </row>
     <row r="214">
@@ -13460,7 +13476,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13521,7 +13537,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13582,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13643,7 +13659,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13704,7 +13720,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13765,7 +13781,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13826,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13948,7 +13964,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14009,7 +14025,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14131,7 +14147,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14162,7 +14178,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>418-5579-CM25</t>
+          <t>655348-101-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14187,12 +14203,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14202,12 +14218,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14217,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2117.68</v>
+        <v>1233.02</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>655348-101-CM25</t>
+          <t>418-5579-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14248,12 +14264,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14263,12 +14279,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14278,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1233.02</v>
+        <v>2117.68</v>
       </c>
     </row>
     <row r="228">
@@ -14314,7 +14330,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14345,7 +14361,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1691-2840-CM25</t>
+          <t>1403-4334-CM25</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14370,12 +14386,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14385,12 +14401,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>TOTAL NUTRITION LIMITADA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>78.048.439-K</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14400,13 +14416,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3090.7</v>
+        <v>5197.97</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1403-4310-CM25</t>
+          <t>1691-3308-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14431,12 +14447,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14446,12 +14462,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>sociedad de nutricionistas nutrihouse ltda.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.095.459-4</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14461,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>827.49</v>
+        <v>9954.01</v>
       </c>
     </row>
     <row r="231">
@@ -14507,7 +14523,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14528,7 +14544,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1691-3308-CM25</t>
+          <t>655348-102-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14553,12 +14569,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14568,12 +14584,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>sociedad de nutricionistas nutrihouse ltda.</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>76.095.459-4</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14583,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>9954.01</v>
+        <v>752.58</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>655348-102-CM25</t>
+          <t>1691-2840-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14614,12 +14630,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14629,12 +14645,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>TOTAL NUTRITION LIMITADA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>78.048.439-K</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14644,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>752.58</v>
+        <v>3090.7</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1403-4334-CM25</t>
+          <t>1403-4310-CM25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14680,7 +14696,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14690,12 +14706,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -14705,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>5197.97</v>
+        <v>827.49</v>
       </c>
     </row>
     <row r="235">
@@ -14741,7 +14757,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14772,7 +14788,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1403-4361-CM25</t>
+          <t>1403-4359-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14802,7 +14818,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14812,12 +14828,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Distribuidora Surmontt</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>76.287.477-6</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14827,13 +14843,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3092.85</v>
+        <v>1705.46</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1403-4360-CM25</t>
+          <t>1403-4361-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14863,7 +14879,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14873,12 +14889,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>Distribuidora Surmontt</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.287.477-6</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -14888,13 +14904,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1705.46</v>
+        <v>3092.85</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1403-4359-CM25</t>
+          <t>1403-4360-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14924,7 +14940,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14985,7 +15001,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15046,7 +15062,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15107,7 +15123,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15168,7 +15184,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15199,7 +15215,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1403-4356-CM25</t>
+          <t>1403-4332-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15229,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15254,13 +15270,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1954.21</v>
+        <v>1022.92</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1403-4332-CM25</t>
+          <t>1403-4356-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15290,7 +15306,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15315,13 +15331,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1022.92</v>
+        <v>1954.21</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1403-4366-CM25</t>
+          <t>1426103-216-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15346,12 +15362,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15361,12 +15377,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -15376,13 +15392,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1651.74</v>
+        <v>2801.78</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1426103-216-CM25</t>
+          <t>1403-4366-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15407,12 +15423,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15422,12 +15438,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15437,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2801.78</v>
+        <v>1651.74</v>
       </c>
     </row>
     <row r="247">
@@ -15565,7 +15581,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1079689-417-CM25</t>
+          <t>1426103-221-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15590,12 +15606,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15605,12 +15621,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15620,13 +15636,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1421.93</v>
+        <v>1487.32</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1426103-221-CM25</t>
+          <t>1079689-417-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15651,12 +15667,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15666,12 +15682,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -15681,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1487.32</v>
+        <v>1421.93</v>
       </c>
     </row>
     <row r="251">
@@ -15778,7 +15794,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15839,7 +15855,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15900,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15961,7 +15977,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16154,7 +16170,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -16459,7 +16475,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -16510,7 +16526,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16571,7 +16587,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16602,7 +16618,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1403-5-CM26</t>
+          <t>1403-7-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16632,7 +16648,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16642,12 +16658,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16657,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>919.88</v>
+        <v>1761.42</v>
       </c>
     </row>
     <row r="267">
@@ -16693,7 +16709,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16724,7 +16740,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1403-7-CM26</t>
+          <t>1403-5-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16754,7 +16770,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16764,12 +16780,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -16779,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1761.42</v>
+        <v>919.88</v>
       </c>
     </row>
     <row r="269">
@@ -16815,7 +16831,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16876,7 +16892,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16937,7 +16953,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -16998,7 +17014,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17059,7 +17075,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17090,7 +17106,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1079689-35-CM26</t>
+          <t>707426-5-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17115,12 +17131,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17145,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1263.5</v>
+        <v>7214.45</v>
       </c>
     </row>
     <row r="275">
@@ -17181,7 +17197,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17212,7 +17228,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>707426-5-CM26</t>
+          <t>1079689-35-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17232,17 +17248,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17267,13 +17283,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>7214.45</v>
+        <v>1263.5</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>418-72-CM26</t>
+          <t>1403-41-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17298,12 +17314,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17313,12 +17329,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -17328,13 +17344,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2640.96</v>
+        <v>3122.41</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1403-41-CM26</t>
+          <t>418-72-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17359,12 +17375,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17374,12 +17390,12 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -17389,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>3122.41</v>
+        <v>2640.96</v>
       </c>
     </row>
     <row r="279">
@@ -17425,7 +17441,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17486,7 +17502,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17547,7 +17563,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17578,7 +17594,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>418-288-CM26</t>
+          <t>1426103-11-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17603,12 +17619,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17618,12 +17634,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -17633,13 +17649,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>3671.54</v>
+        <v>1908.91</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1426103-12-CM26</t>
+          <t>1173435-5-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17664,12 +17680,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>73.182.900-4</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17679,12 +17695,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -17694,13 +17710,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>3238.19</v>
+        <v>1300.03</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1426103-11-CM26</t>
+          <t>1426103-12-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17740,12 +17756,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17755,13 +17771,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1908.91</v>
+        <v>3238.19</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1173435-5-CM26</t>
+          <t>418-288-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17786,12 +17802,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>73.182.900-4</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17816,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>1300.03</v>
+        <v>3671.54</v>
       </c>
     </row>
     <row r="286">
@@ -17852,7 +17868,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17944,7 +17960,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>707426-11-CM26</t>
+          <t>1079689-50-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17969,12 +17985,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -17984,12 +18000,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K288" t="inlineStr"/>
@@ -17999,13 +18015,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1133.5</v>
+        <v>2511.83</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>707426-12-CM26</t>
+          <t>707426-11-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18045,12 +18061,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
@@ -18060,13 +18076,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1058.11</v>
+        <v>1133.5</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1079689-50-CM26</t>
+          <t>707426-12-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18091,12 +18107,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18106,12 +18122,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18121,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2511.83</v>
+        <v>1058.11</v>
       </c>
     </row>
     <row r="291">
@@ -18157,7 +18173,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18188,7 +18204,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>418-326-CM26</t>
+          <t>418-324-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18208,7 +18224,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -18228,12 +18244,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18243,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2192.28</v>
+        <v>2710.68</v>
       </c>
     </row>
     <row r="293">
@@ -18310,7 +18326,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>418-324-CM26</t>
+          <t>418-326-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18330,7 +18346,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -18350,12 +18366,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18365,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2710.68</v>
+        <v>2192.28</v>
       </c>
     </row>
     <row r="295">
@@ -18401,7 +18417,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18462,7 +18478,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18493,7 +18509,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1403-83-CM26</t>
+          <t>1403-86-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18523,7 +18539,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18548,13 +18564,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3811.52</v>
+        <v>1931.72</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1403-84-CM26</t>
+          <t>1403-85-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18584,7 +18600,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18594,12 +18610,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -18609,13 +18625,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>856.3099999999999</v>
+        <v>3035.22</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1403-85-CM26</t>
+          <t>1403-84-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18645,7 +18661,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18655,12 +18671,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -18670,13 +18686,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>3035.22</v>
+        <v>856.3099999999999</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1403-86-CM26</t>
+          <t>1403-83-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18706,7 +18722,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18731,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1931.72</v>
+        <v>3811.52</v>
       </c>
     </row>
     <row r="301">
@@ -19021,7 +19037,7 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
@@ -19143,7 +19159,7 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -19164,7 +19180,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1403-121-CM26</t>
+          <t>1403-124-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19194,7 +19210,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19204,12 +19220,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19219,13 +19235,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2675.24</v>
+        <v>2462.68</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1403-124-CM26</t>
+          <t>1403-120-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19255,7 +19271,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19280,13 +19296,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2462.68</v>
+        <v>2389.09</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1403-120-CM26</t>
+          <t>1403-121-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19316,7 +19332,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19326,12 +19342,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19341,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2389.09</v>
+        <v>2675.24</v>
       </c>
     </row>
     <row r="311">
@@ -19438,7 +19454,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19499,7 +19515,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19560,7 +19576,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19621,7 +19637,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19682,7 +19698,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19713,7 +19729,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1173437-3-CM26</t>
+          <t>1079689-81-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19738,12 +19754,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>61.959.200-K</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19753,12 +19769,12 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -19768,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>3172.99</v>
+        <v>2758.73</v>
       </c>
     </row>
     <row r="318">
@@ -19814,7 +19830,7 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
@@ -19835,7 +19851,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1079689-81-CM26</t>
+          <t>1173437-3-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19860,12 +19876,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.959.200-K</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19875,12 +19891,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K319" t="inlineStr"/>
@@ -19890,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2758.73</v>
+        <v>3172.99</v>
       </c>
     </row>
     <row r="320">
@@ -19926,7 +19942,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -19957,7 +19973,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1403-137-CM26</t>
+          <t>3431-24-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -19982,12 +19998,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -19997,12 +20013,12 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K321" t="inlineStr"/>
@@ -20012,13 +20028,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>809.09</v>
+        <v>18145.11</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>655348-27-CM26</t>
+          <t>3431-25-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20043,12 +20059,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20058,12 +20074,12 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K322" t="inlineStr"/>
@@ -20073,13 +20089,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2050.51</v>
+        <v>3104.49</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1403-138-CM26</t>
+          <t>655348-27-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20104,12 +20120,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20119,12 +20135,12 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K323" t="inlineStr"/>
@@ -20134,13 +20150,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>999.53</v>
+        <v>2050.51</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>3431-24-CM26</t>
+          <t>1403-137-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20165,12 +20181,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20180,12 +20196,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K324" t="inlineStr"/>
@@ -20195,13 +20211,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>18145.11</v>
+        <v>809.09</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>3431-25-CM26</t>
+          <t>1403-138-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20226,12 +20242,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20241,12 +20257,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -20256,13 +20272,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>3104.49</v>
+        <v>999.53</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>3431-34-CM26</t>
+          <t>3431-33-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20292,7 +20308,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20302,12 +20318,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>Distribuidora Surmontt</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>76.287.477-6</t>
         </is>
       </c>
       <c r="K326" t="inlineStr"/>
@@ -20317,13 +20333,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>4911.68</v>
+        <v>1441.63</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>3431-36-CM26</t>
+          <t>3431-34-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20353,7 +20369,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20378,13 +20394,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>2726.79</v>
+        <v>4911.68</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>3431-33-CM26</t>
+          <t>3431-36-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20414,7 +20430,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20424,12 +20440,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Distribuidora Surmontt</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>76.287.477-6</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K328" t="inlineStr"/>
@@ -20439,13 +20455,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1441.63</v>
+        <v>2726.79</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1403-153-CM26</t>
+          <t>1079689-92-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -20470,12 +20486,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20485,12 +20501,12 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K329" t="inlineStr"/>
@@ -20500,13 +20516,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1948.08</v>
+        <v>8134.89</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1403-154-CM26</t>
+          <t>1403-153-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -20536,7 +20552,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20546,12 +20562,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K330" t="inlineStr"/>
@@ -20561,13 +20577,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2363.98</v>
+        <v>1948.08</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1079689-92-CM26</t>
+          <t>1403-154-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -20592,12 +20608,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20607,12 +20623,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K331" t="inlineStr"/>
@@ -20622,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>8134.89</v>
+        <v>2363.98</v>
       </c>
     </row>
     <row r="332">
@@ -20658,7 +20674,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20719,7 +20735,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20750,7 +20766,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>4778-93-CM26</t>
+          <t>4778-92-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -20790,12 +20806,12 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K334" t="inlineStr"/>
@@ -20805,13 +20821,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1250.18</v>
+        <v>1889.67</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>4778-92-CM26</t>
+          <t>4778-93-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -20851,12 +20867,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K335" t="inlineStr"/>
@@ -20866,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1889.67</v>
+        <v>1250.18</v>
       </c>
     </row>
     <row r="336">
@@ -20902,7 +20918,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -20963,7 +20979,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21024,7 +21040,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21146,7 +21162,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21207,7 +21223,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21278,7 +21294,7 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
@@ -21329,7 +21345,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21360,7 +21376,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1079689-119-CM26</t>
+          <t>1079689-118-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21380,7 +21396,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -21390,7 +21406,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21400,12 +21416,12 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K344" t="inlineStr"/>
@@ -21415,13 +21431,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>4874.2</v>
+        <v>4572.71</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1426103-25-CM26</t>
+          <t>1079689-119-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21446,12 +21462,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21461,12 +21477,12 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K345" t="inlineStr"/>
@@ -21476,13 +21492,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2330.34</v>
+        <v>4874.2</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1079689-118-CM26</t>
+          <t>1426103-25-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -21502,17 +21518,17 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21522,12 +21538,12 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K346" t="inlineStr"/>
@@ -21537,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>4572.71</v>
+        <v>2330.34</v>
       </c>
     </row>
     <row r="347">
@@ -21573,7 +21589,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21604,7 +21620,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1691-530-CM26</t>
+          <t>1403-225-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21629,12 +21645,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21644,12 +21660,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -21659,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>766.13</v>
+        <v>775.6799999999999</v>
       </c>
     </row>
     <row r="349">
@@ -21695,7 +21711,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21726,7 +21742,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1403-225-CM26</t>
+          <t>1691-530-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -21751,12 +21767,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21766,12 +21782,12 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K350" t="inlineStr"/>
@@ -21781,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>775.6799999999999</v>
+        <v>766.13</v>
       </c>
     </row>
     <row r="351">
@@ -21817,7 +21833,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -21878,7 +21894,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -21939,7 +21955,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -21970,7 +21986,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>951405-84-CM26</t>
+          <t>4778-94-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -21995,12 +22011,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22010,12 +22026,12 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K354" t="inlineStr"/>
@@ -22025,13 +22041,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>68618.61</v>
+        <v>6400.23</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>4778-94-CM26</t>
+          <t>951405-84-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22056,12 +22072,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22071,12 +22087,12 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K355" t="inlineStr"/>
@@ -22086,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>6400.23</v>
+        <v>68618.61</v>
       </c>
     </row>
     <row r="356">
@@ -22122,7 +22138,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -22183,7 +22199,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -22214,7 +22230,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1426103-29-CM26</t>
+          <t>1079689-140-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22239,12 +22255,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -22254,12 +22270,12 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K358" t="inlineStr"/>
@@ -22269,13 +22285,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2012.69</v>
+        <v>2359.13</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1426103-30-CM26</t>
+          <t>1173437-5-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22300,12 +22316,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.959.200-K</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22315,12 +22331,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>BIDFOOD CHILE S.A.</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.111.152-3</t>
         </is>
       </c>
       <c r="K359" t="inlineStr"/>
@@ -22330,13 +22346,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1181.96</v>
+        <v>3360.33</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1173437-5-CM26</t>
+          <t>1426103-30-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22361,12 +22377,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.959.200-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22376,12 +22392,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>BIDFOOD CHILE S.A.</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>76.111.152-3</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K360" t="inlineStr"/>
@@ -22391,13 +22407,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>3360.33</v>
+        <v>1181.96</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1079689-140-CM26</t>
+          <t>1426103-29-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -22422,12 +22438,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -22437,12 +22453,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K361" t="inlineStr"/>
@@ -22452,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>2359.13</v>
+        <v>2012.69</v>
       </c>
     </row>
     <row r="362">
@@ -22488,7 +22504,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -22519,7 +22535,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1403-265-CM26</t>
+          <t>1403-261-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -22549,7 +22565,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22559,12 +22575,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -22574,13 +22590,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2485.16</v>
+        <v>802.96</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1403-261-CM26</t>
+          <t>1403-265-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -22610,7 +22626,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -22620,12 +22636,12 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K364" t="inlineStr"/>
@@ -22635,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>802.96</v>
+        <v>2485.16</v>
       </c>
     </row>
     <row r="365">
@@ -22742,7 +22758,7 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -22793,7 +22809,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -22854,7 +22870,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -22925,7 +22941,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -22976,7 +22992,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23037,7 +23053,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23098,7 +23114,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23159,7 +23175,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23220,7 +23236,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23251,7 +23267,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1426103-35-CM26</t>
+          <t>1426103-34-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23291,12 +23307,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K375" t="inlineStr"/>
@@ -23306,13 +23322,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>1495.22</v>
+        <v>2470.17</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1426103-34-CM26</t>
+          <t>1426103-35-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -23352,12 +23368,12 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K376" t="inlineStr"/>
@@ -23367,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>2470.17</v>
+        <v>1495.22</v>
       </c>
     </row>
     <row r="377">
@@ -23403,7 +23419,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -23464,7 +23480,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -23495,7 +23511,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1403-315-CM26</t>
+          <t>1403-334-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -23525,7 +23541,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -23535,12 +23551,12 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K379" t="inlineStr"/>
@@ -23550,13 +23566,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1856.9</v>
+        <v>1944.01</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1403-317-CM26</t>
+          <t>1403-318-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -23586,7 +23602,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -23596,12 +23612,12 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K380" t="inlineStr"/>
@@ -23611,13 +23627,13 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>1889.97</v>
+        <v>2932.24</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1403-318-CM26</t>
+          <t>1403-317-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -23647,7 +23663,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -23657,12 +23673,12 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K381" t="inlineStr"/>
@@ -23672,13 +23688,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2932.24</v>
+        <v>1889.97</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1403-334-CM26</t>
+          <t>1403-315-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -23708,7 +23724,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -23718,12 +23734,12 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K382" t="inlineStr"/>
@@ -23733,13 +23749,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1944.01</v>
+        <v>1856.9</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>951405-142-CM26</t>
+          <t>418-1466-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -23764,12 +23780,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -23779,12 +23795,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K383" t="inlineStr"/>
@@ -23794,13 +23810,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>20590.29</v>
+        <v>2271.17</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>951405-145-CM26</t>
+          <t>951405-142-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -23830,7 +23846,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -23840,12 +23856,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K384" t="inlineStr"/>
@@ -23855,13 +23871,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>3321.48</v>
+        <v>20590.29</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>418-1466-CM26</t>
+          <t>951405-145-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -23886,12 +23902,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -23901,12 +23917,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K385" t="inlineStr"/>
@@ -23916,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>2271.17</v>
+        <v>3321.48</v>
       </c>
     </row>
     <row r="386">
@@ -23952,7 +23968,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24084,7 +24100,7 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
@@ -24166,7 +24182,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1403-351-CM26</t>
+          <t>655348-50-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -24191,12 +24207,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24206,12 +24222,12 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K390" t="inlineStr"/>
@@ -24221,13 +24237,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>3489.14</v>
+        <v>1042.17</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>655348-50-CM26</t>
+          <t>1403-351-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -24252,12 +24268,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -24267,12 +24283,12 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K391" t="inlineStr"/>
@@ -24282,13 +24298,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>1042.17</v>
+        <v>3489.14</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1173435-22-CM26</t>
+          <t>1403-354-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -24313,12 +24329,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>73.182.900-4</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -24328,12 +24344,12 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K392" t="inlineStr"/>
@@ -24343,13 +24359,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1759.43</v>
+        <v>1898.98</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1403-354-CM26</t>
+          <t>1173435-22-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -24374,12 +24390,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>73.182.900-4</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24389,12 +24405,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K393" t="inlineStr"/>
@@ -24404,13 +24420,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>1898.98</v>
+        <v>1759.43</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1403-367-CM26</t>
+          <t>4778-292-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -24435,12 +24451,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -24450,12 +24466,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K394" t="inlineStr"/>
@@ -24465,13 +24481,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>1768.65</v>
+        <v>7844.22</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>4778-292-CM26</t>
+          <t>1403-367-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -24496,12 +24512,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24511,12 +24527,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K395" t="inlineStr"/>
@@ -24526,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>7844.22</v>
+        <v>1768.65</v>
       </c>
     </row>
     <row r="396">
@@ -24623,7 +24639,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -24684,7 +24700,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -24745,7 +24761,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -24806,7 +24822,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -24877,7 +24893,7 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
@@ -24898,7 +24914,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1426103-49-CM26</t>
+          <t>1426103-48-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -24938,12 +24954,12 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K402" t="inlineStr"/>
@@ -24953,13 +24969,13 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2136.34</v>
+        <v>1014.34</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1426103-48-CM26</t>
+          <t>1426103-49-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -24999,12 +25015,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K403" t="inlineStr"/>
@@ -25014,13 +25030,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>1014.34</v>
+        <v>2136.34</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1403-412-CM26</t>
+          <t>1403-410-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -25050,7 +25066,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25060,12 +25076,12 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K404" t="inlineStr"/>
@@ -25075,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>2206.64</v>
+        <v>2750.3</v>
       </c>
     </row>
     <row r="405">
@@ -25111,7 +25127,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -25142,7 +25158,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1403-410-CM26</t>
+          <t>1403-412-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -25172,7 +25188,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25182,12 +25198,12 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K406" t="inlineStr"/>
@@ -25197,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>2750.3</v>
+        <v>2206.64</v>
       </c>
     </row>
     <row r="407">
@@ -25233,7 +25249,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -25294,7 +25310,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -25355,7 +25371,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -25416,7 +25432,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -25477,7 +25493,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -25508,7 +25524,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1426103-54-CM26</t>
+          <t>418-1865-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -25528,17 +25544,17 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25548,12 +25564,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K412" t="inlineStr"/>
@@ -25563,13 +25579,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1426.23</v>
+        <v>1108.85</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1426103-53-CM26</t>
+          <t>951405-225-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -25589,17 +25605,17 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -25609,12 +25625,12 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K413" t="inlineStr"/>
@@ -25624,13 +25640,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1660.73</v>
+        <v>9234.690000000001</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1426103-52-CM26</t>
+          <t>951405-227-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -25655,12 +25671,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -25670,12 +25686,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K414" t="inlineStr"/>
@@ -25685,13 +25701,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>3111.37</v>
+        <v>948.72</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1426103-51-CM26</t>
+          <t>655348-54-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -25716,12 +25732,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -25731,12 +25747,12 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVIVAC LTDA</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.607.200-8</t>
         </is>
       </c>
       <c r="K415" t="inlineStr"/>
@@ -25746,13 +25762,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>6335.87</v>
+        <v>1117.48</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>951405-227-CM26</t>
+          <t>1426103-51-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -25777,12 +25793,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -25792,12 +25808,12 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K416" t="inlineStr"/>
@@ -25807,13 +25823,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>948.72</v>
+        <v>6335.87</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>951405-225-CM26</t>
+          <t>1426103-52-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -25838,12 +25854,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -25853,12 +25869,12 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K417" t="inlineStr"/>
@@ -25868,13 +25884,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>9234.690000000001</v>
+        <v>3111.37</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>418-1865-CM26</t>
+          <t>1426103-53-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -25894,17 +25910,17 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -25914,12 +25930,12 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K418" t="inlineStr"/>
@@ -25929,13 +25945,13 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>1108.85</v>
+        <v>1660.73</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>655348-54-CM26</t>
+          <t>1426103-54-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -25955,17 +25971,17 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -25975,12 +25991,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>PROVIVAC LTDA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>96.607.200-8</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K419" t="inlineStr"/>
@@ -25990,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1117.48</v>
+        <v>1426.23</v>
       </c>
     </row>
     <row r="420">
@@ -26026,7 +26042,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -26087,7 +26103,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -26148,7 +26164,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -26209,7 +26225,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -26240,7 +26256,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>4778-308-CM26</t>
+          <t>4778-324-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -26280,12 +26296,12 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>sociedad de nutricionistas nutrihouse ltda.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>76.095.459-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K424" t="inlineStr"/>
@@ -26295,13 +26311,13 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>2145.56</v>
+        <v>4929.83</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>4778-307-CM26</t>
+          <t>4778-308-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -26341,12 +26357,12 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>sociedad de nutricionistas nutrihouse ltda.</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>76.095.459-4</t>
         </is>
       </c>
       <c r="K425" t="inlineStr"/>
@@ -26356,13 +26372,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>4231.2</v>
+        <v>2145.56</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>4778-324-CM26</t>
+          <t>4778-307-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -26402,12 +26418,12 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K426" t="inlineStr"/>
@@ -26417,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>4929.83</v>
+        <v>4231.2</v>
       </c>
     </row>
     <row r="427">
@@ -26514,7 +26530,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -26575,7 +26591,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -26636,7 +26652,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -26667,7 +26683,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>1426103-62-CM26</t>
+          <t>1426103-60-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -26707,12 +26723,12 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>BIDFOOD CHILE S.A.</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.111.152-3</t>
         </is>
       </c>
       <c r="K431" t="inlineStr"/>
@@ -26722,13 +26738,13 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1938.63</v>
+        <v>787.26</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>1426103-60-CM26</t>
+          <t>1426103-61-CM26</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -26768,12 +26784,12 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>BIDFOOD CHILE S.A.</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>76.111.152-3</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K432" t="inlineStr"/>
@@ -26783,13 +26799,13 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>787.26</v>
+        <v>1129.65</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>1426103-61-CM26</t>
+          <t>1426103-62-CM26</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -26829,12 +26845,12 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K433" t="inlineStr"/>
@@ -26844,13 +26860,13 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>1129.65</v>
+        <v>1938.63</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>418-2153-CM26</t>
+          <t>1403-516-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -26875,12 +26891,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -26890,12 +26906,12 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K434" t="inlineStr"/>
@@ -26905,13 +26921,13 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>841.92</v>
+        <v>776.46</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>418-2167-CM26</t>
+          <t>418-2153-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -26951,12 +26967,12 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K435" t="inlineStr"/>
@@ -26966,13 +26982,13 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>2290.08</v>
+        <v>841.92</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>1403-516-CM26</t>
+          <t>418-2167-CM26</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -26997,12 +27013,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27027,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>776.46</v>
+        <v>2290.08</v>
       </c>
     </row>
     <row r="437">
@@ -27063,7 +27079,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27124,7 +27140,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27155,7 +27171,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1403-534-CM26</t>
+          <t>1403-530-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -27185,7 +27201,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27195,12 +27211,12 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K439" t="inlineStr"/>
@@ -27210,13 +27226,13 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2895.55</v>
+        <v>3777.09</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>1426103-64-CM26</t>
+          <t>1403-531-CM26</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -27241,12 +27257,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27271,13 +27287,13 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>1123.11</v>
+        <v>841.77</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>1403-530-CM26</t>
+          <t>1403-534-CM26</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -27307,7 +27323,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -27317,12 +27333,12 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K441" t="inlineStr"/>
@@ -27332,13 +27348,13 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>3777.09</v>
+        <v>2895.55</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>1403-531-CM26</t>
+          <t>1426103-64-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -27363,12 +27379,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -27393,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>841.77</v>
+        <v>1123.11</v>
       </c>
     </row>
     <row r="443">
@@ -27429,7 +27445,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -27490,7 +27506,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -27521,7 +27537,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>3431-121-CM26</t>
+          <t>1403-544-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -27546,12 +27562,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -27576,13 +27592,13 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>1277.81</v>
+        <v>775.5</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>1403-544-CM26</t>
+          <t>3431-121-CM26</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -27607,12 +27623,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -27637,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>775.5</v>
+        <v>1277.81</v>
       </c>
     </row>
     <row r="447">
@@ -27673,7 +27689,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -27724,7 +27740,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -27734,7 +27750,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -27795,7 +27811,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -27856,7 +27872,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -27917,7 +27933,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -27948,7 +27964,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>1403-602-CM26</t>
+          <t>1403-587-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -27978,7 +27994,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -27988,12 +28004,12 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K452" t="inlineStr"/>
@@ -28003,13 +28019,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>773.66</v>
+        <v>4099.96</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1403-588-CM26</t>
+          <t>1173437-14-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -28034,12 +28050,12 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.959.200-K</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -28049,12 +28065,12 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>BIDFOOD CHILE S.A.</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.111.152-3</t>
         </is>
       </c>
       <c r="K453" t="inlineStr"/>
@@ -28064,13 +28080,13 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>2223.79</v>
+        <v>2158.04</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>1173437-14-CM26</t>
+          <t>1403-588-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -28095,12 +28111,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>61.959.200-K</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Puerto Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -28110,12 +28126,12 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>BIDFOOD CHILE S.A.</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>76.111.152-3</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K454" t="inlineStr"/>
@@ -28125,13 +28141,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>2158.04</v>
+        <v>2223.79</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>1403-587-CM26</t>
+          <t>1403-602-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -28161,7 +28177,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -28171,12 +28187,12 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K455" t="inlineStr"/>
@@ -28186,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>4099.96</v>
+        <v>773.66</v>
       </c>
     </row>
     <row r="456">
@@ -28222,7 +28238,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -28273,7 +28289,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -28283,7 +28299,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -28334,7 +28350,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
@@ -28344,7 +28360,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -28395,7 +28411,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -28405,7 +28421,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -28456,7 +28472,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -28466,7 +28482,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -28802,7 +28818,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>1079689-334-CM26</t>
+          <t>4778-448-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -28827,12 +28843,12 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -28842,12 +28858,12 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K466" t="inlineStr"/>
@@ -28857,13 +28873,13 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>4629.81</v>
+        <v>1831.27</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>1403-620-CM26</t>
+          <t>1403-621-CM26</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -28903,12 +28919,12 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>COMERCIAL SURMIX SPA</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>77.145.084-9</t>
         </is>
       </c>
       <c r="K467" t="inlineStr"/>
@@ -28918,13 +28934,13 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>1900.76</v>
+        <v>3064.2</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>1403-621-CM26</t>
+          <t>1079689-334-CM26</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -28949,12 +28965,12 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -28964,12 +28980,12 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>COMERCIAL SURMIX SPA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>77.145.084-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K468" t="inlineStr"/>
@@ -28979,13 +28995,13 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>3064.2</v>
+        <v>4629.81</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>4778-448-CM26</t>
+          <t>1403-620-CM26</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -29010,12 +29026,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -29025,12 +29041,12 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K469" t="inlineStr"/>
@@ -29040,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>1831.27</v>
+        <v>1900.76</v>
       </c>
     </row>
     <row r="470">
@@ -29107,7 +29123,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>1079689-350-CM26</t>
+          <t>1403-644-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -29132,12 +29148,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -29147,12 +29163,12 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K471" t="inlineStr"/>
@@ -29162,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>2411.11</v>
+        <v>1764.06</v>
       </c>
     </row>
     <row r="472">
@@ -29229,7 +29245,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>1403-644-CM26</t>
+          <t>1079689-350-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -29254,12 +29270,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -29269,12 +29285,12 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K473" t="inlineStr"/>
@@ -29284,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>1764.06</v>
+        <v>2411.11</v>
       </c>
     </row>
     <row r="474">
@@ -29412,7 +29428,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>1173437-16-CM26</t>
+          <t>1403-665-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -29437,7 +29453,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>61.959.200-K</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -29452,12 +29468,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>BIDFOOD CHILE S.A.</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>76.111.152-3</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K476" t="inlineStr"/>
@@ -29467,13 +29483,13 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>3232.46</v>
+        <v>954.38</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>1403-665-CM26</t>
+          <t>418-2728-CM26</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -29498,12 +29514,12 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29513,12 +29529,12 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K477" t="inlineStr"/>
@@ -29528,13 +29544,13 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>954.38</v>
+        <v>1738.34</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>418-2728-CM26</t>
+          <t>1173437-16-CM26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -29559,12 +29575,12 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.959.200-K</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -29574,12 +29590,12 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>BIDFOOD CHILE S.A.</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>76.111.152-3</t>
         </is>
       </c>
       <c r="K478" t="inlineStr"/>
@@ -29589,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>1738.34</v>
+        <v>3232.46</v>
       </c>
     </row>
     <row r="479">
@@ -29717,7 +29733,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>1403-684-CM26</t>
+          <t>1403-678-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -29757,12 +29773,12 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K481" t="inlineStr"/>
@@ -29772,13 +29788,13 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>1564.89</v>
+        <v>1924.35</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1403-678-CM26</t>
+          <t>1403-684-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -29818,12 +29834,12 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K482" t="inlineStr"/>
@@ -29833,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>1924.35</v>
+        <v>1564.89</v>
       </c>
     </row>
     <row r="483">
@@ -29920,7 +29936,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -29981,7 +29997,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -30017,6 +30033,1409 @@
       </c>
       <c r="M485" s="2" t="n">
         <v>1225.74</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>1173435-32-CM26</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>73.182.900-4</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M486" s="2" t="n">
+        <v>2147.63</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>1403-706-CM26</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>79.984.240-8</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M487" s="2" t="n">
+        <v>1046.04</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>1403-702-CM26</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>81.094.100-6</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M488" s="2" t="n">
+        <v>1637.06</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>1403-724-CM26</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M489" s="2" t="n">
+        <v>1499.96</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>1403-725-CM26</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>BIDFOOD CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>76.111.152-3</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M490" s="2" t="n">
+        <v>2581.82</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>1173437-19-CM26</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>61.959.200-K</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>BIDFOOD CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>76.111.152-3</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M491" s="2" t="n">
+        <v>1922.3</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>1403-727-CM26</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>79.984.240-8</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M492" s="2" t="n">
+        <v>797.78</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>1426103-83-CM26</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>79.984.240-8</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M493" s="2" t="n">
+        <v>2608.5</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>1426103-84-CM26</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>81.094.100-6</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M494" s="2" t="n">
+        <v>1373.68</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>1426103-85-CM26</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rodolfo </t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>76.888.569-9</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M495" s="2" t="n">
+        <v>1126.84</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2713-1012-CM26</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M496" s="2" t="n">
+        <v>1870.95</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>1403-731-CM26</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>79.984.240-8</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M497" s="2" t="n">
+        <v>1766.88</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>1403-740-CM26</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>79.984.240-8</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M498" s="2" t="n">
+        <v>1325.03</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>1403-749-CM26</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>79.984.240-8</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M499" s="2" t="n">
+        <v>853.59</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>3431-140-CM26</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>61.101.085-0</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>79.984.240-8</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M500" s="2" t="n">
+        <v>760.53</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>3431-141-CM26</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>61.101.085-0</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>PROVIVAC LTDA</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>96.607.200-8</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M501" s="2" t="n">
+        <v>5352.03</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>1403-762-CM26</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M502" s="2" t="n">
+        <v>3909.31</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>1403-774-CM26</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>79.984.240-8</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M503" s="2" t="n">
+        <v>3564.96</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>1403-768-CM26</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M504" s="2" t="n">
+        <v>804.26</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>1403-769-CM26</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>81.094.100-6</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M505" s="2" t="n">
+        <v>1833.56</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>418-3236-CM26</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M506" s="2" t="n">
+        <v>1824.57</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>418-3223-CM26</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M507" s="2" t="n">
+        <v>1236.33</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>418-3239-CM26</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>79.984.240-8</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M508" s="2" t="n">
+        <v>805.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/alimentos/aysen.xlsx
+++ b/docs/oc-regiones/alimentos/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1001,7 +1005,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1558,7 +1566,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1867,7 +1879,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1928,7 +1944,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2233,7 +2253,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2672,7 +2696,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2733,7 +2761,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2916,7 +2948,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2977,7 +3013,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3473,7 +3513,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3904,7 +3948,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4148,7 +4196,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4888,7 +4940,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4949,7 +5005,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5010,7 +5070,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5071,7 +5135,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5197,7 +5265,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5258,7 +5330,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5384,7 +5460,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5823,7 +5903,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5884,7 +5968,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5945,7 +6033,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6762,7 +6854,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6884,7 +6980,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7071,7 +7171,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7132,7 +7236,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7254,7 +7362,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7559,7 +7671,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7620,7 +7736,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7803,7 +7923,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7864,7 +7988,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8177,7 +8305,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8299,7 +8431,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8360,7 +8496,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8543,7 +8683,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8604,7 +8748,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8730,7 +8878,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8852,7 +9004,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8974,7 +9130,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9539,7 +9699,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9726,7 +9890,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10039,7 +10207,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10100,7 +10272,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10161,7 +10337,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10222,7 +10402,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10283,7 +10467,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10405,7 +10593,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10466,7 +10658,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10649,7 +10845,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11145,7 +11345,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11645,7 +11849,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11771,7 +11979,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11893,7 +12105,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12015,7 +12231,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12442,7 +12662,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12629,7 +12853,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12751,7 +12979,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12812,7 +13044,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13056,7 +13292,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13182,7 +13422,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13495,7 +13739,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13621,7 +13869,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14003,7 +14255,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14064,7 +14320,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14308,7 +14568,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14495,7 +14759,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14804,7 +15072,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15048,7 +15320,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15170,7 +15446,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15296,7 +15576,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15544,7 +15828,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15788,7 +16076,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16231,7 +16523,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16292,7 +16588,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17088,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17153,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17283,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17166,7 +17478,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17227,7 +17543,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17288,7 +17608,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17410,7 +17734,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17593,7 +17921,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17654,7 +17986,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17902,7 +18238,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18085,7 +18425,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18272,7 +18616,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18455,7 +18803,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18703,7 +19055,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19508,7 +19864,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19691,7 +20051,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19752,7 +20116,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19813,7 +20181,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19874,7 +20246,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19996,7 +20372,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20427,7 +20807,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20549,7 +20933,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20610,7 +20998,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21106,7 +21498,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21289,7 +21685,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21533,7 +21933,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21594,7 +21998,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22033,7 +22441,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22155,7 +22567,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22521,7 +22937,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22704,7 +23124,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22765,7 +23189,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22952,7 +23380,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23074,7 +23506,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23257,7 +23693,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23509,7 +23949,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23753,7 +24197,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23875,7 +24323,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24001,7 +24453,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24127,7 +24583,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24249,7 +24709,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24619,7 +25083,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24745,7 +25213,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25184,7 +25656,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25310,7 +25786,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25554,7 +26034,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25802,7 +26286,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25985,7 +26473,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26172,7 +26664,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26355,7 +26851,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26416,7 +26916,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26794,7 +27298,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26977,7 +27485,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27221,7 +27733,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27282,7 +27798,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27469,7 +27989,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27652,7 +28176,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27713,7 +28241,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27835,7 +28367,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27957,7 +28493,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28144,7 +28684,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28205,7 +28749,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28518,7 +29066,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28888,7 +29440,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29197,7 +29753,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29258,7 +29818,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29319,7 +29883,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29624,7 +30192,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29685,7 +30257,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29990,7 +30566,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30112,7 +30692,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30429,7 +31013,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31002,7 +31590,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31311,7 +31903,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31494,7 +32090,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31616,7 +32216,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31677,7 +32281,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31738,7 +32346,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31799,7 +32411,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31921,7 +32537,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32165,7 +32785,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32226,7 +32850,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32287,7 +32915,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32535,7 +33167,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32722,7 +33358,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32970,7 +33610,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33092,7 +33736,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33462,7 +34110,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33523,7 +34175,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33832,7 +34488,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34080,7 +34740,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34324,7 +34988,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34568,7 +35236,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34629,7 +35301,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34877,7 +35553,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35121,7 +35801,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35247,7 +35931,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35430,7 +36118,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35491,7 +36183,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35552,7 +36248,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35613,7 +36313,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35800,7 +36504,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36109,7 +36817,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/alimentos/aysen.xlsx
+++ b/docs/oc-regiones/alimentos/aysen.xlsx
@@ -31046,7 +31046,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -31111,7 +31111,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -33078,7 +33078,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -33143,7 +33143,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
@@ -33204,7 +33204,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
@@ -33517,7 +33517,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
